--- a/artfynd/A 23143-2024 artfynd.xlsx
+++ b/artfynd/A 23143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902885</v>
       </c>
       <c r="B2" t="n">
-        <v>105908</v>
+        <v>105915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902891</v>
       </c>
       <c r="B3" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125902848</v>
       </c>
       <c r="B4" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125902861</v>
       </c>
       <c r="B5" t="n">
-        <v>103755</v>
+        <v>103762</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23143-2024 artfynd.xlsx
+++ b/artfynd/A 23143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902885</v>
       </c>
       <c r="B2" t="n">
-        <v>105915</v>
+        <v>105916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902891</v>
       </c>
       <c r="B3" t="n">
-        <v>100513</v>
+        <v>100514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125902848</v>
       </c>
       <c r="B4" t="n">
-        <v>100420</v>
+        <v>100421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125902861</v>
       </c>
       <c r="B5" t="n">
-        <v>103762</v>
+        <v>103763</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23143-2024 artfynd.xlsx
+++ b/artfynd/A 23143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902885</v>
       </c>
       <c r="B2" t="n">
-        <v>105916</v>
+        <v>105918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902891</v>
       </c>
       <c r="B3" t="n">
-        <v>100514</v>
+        <v>100516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125902848</v>
       </c>
       <c r="B4" t="n">
-        <v>100421</v>
+        <v>100423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125902861</v>
       </c>
       <c r="B5" t="n">
-        <v>103763</v>
+        <v>103765</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23143-2024 artfynd.xlsx
+++ b/artfynd/A 23143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902885</v>
       </c>
       <c r="B2" t="n">
-        <v>105918</v>
+        <v>105922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902891</v>
       </c>
       <c r="B3" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125902848</v>
       </c>
       <c r="B4" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125902861</v>
       </c>
       <c r="B5" t="n">
-        <v>103765</v>
+        <v>103769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23143-2024 artfynd.xlsx
+++ b/artfynd/A 23143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902885</v>
       </c>
       <c r="B2" t="n">
-        <v>105922</v>
+        <v>105923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902891</v>
       </c>
       <c r="B3" t="n">
-        <v>100520</v>
+        <v>100521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125902848</v>
       </c>
       <c r="B4" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125902861</v>
       </c>
       <c r="B5" t="n">
-        <v>103769</v>
+        <v>103770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23143-2024 artfynd.xlsx
+++ b/artfynd/A 23143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902885</v>
       </c>
       <c r="B2" t="n">
-        <v>105923</v>
+        <v>105925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lennart Persson, Magnus Thorell</t>
+          <t>Magnus Thorell, Lennart Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +780,7 @@
         <v>125902891</v>
       </c>
       <c r="B3" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lennart Persson, Magnus Thorell</t>
+          <t>Magnus Thorell, Lennart Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>125902848</v>
       </c>
       <c r="B4" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lennart Persson, Magnus Thorell</t>
+          <t>Magnus Thorell, Lennart Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -993,7 +993,7 @@
         <v>125902861</v>
       </c>
       <c r="B5" t="n">
-        <v>103770</v>
+        <v>103772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lennart Persson, Magnus Thorell</t>
+          <t>Magnus Thorell, Lennart Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 23143-2024 artfynd.xlsx
+++ b/artfynd/A 23143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902885</v>
       </c>
       <c r="B2" t="n">
-        <v>105925</v>
+        <v>105927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902891</v>
       </c>
       <c r="B3" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125902848</v>
       </c>
       <c r="B4" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Thorell, Lennart Persson</t>
+          <t>Lennart Persson, Magnus Thorell</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -993,7 +993,7 @@
         <v>125902861</v>
       </c>
       <c r="B5" t="n">
-        <v>103772</v>
+        <v>103774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23143-2024 artfynd.xlsx
+++ b/artfynd/A 23143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902885</v>
       </c>
       <c r="B2" t="n">
-        <v>105927</v>
+        <v>105931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Thorell, Lennart Persson</t>
+          <t>Lennart Persson, Magnus Thorell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +780,7 @@
         <v>125902891</v>
       </c>
       <c r="B3" t="n">
-        <v>100525</v>
+        <v>100527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Thorell, Lennart Persson</t>
+          <t>Lennart Persson, Magnus Thorell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>125902848</v>
       </c>
       <c r="B4" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125902861</v>
       </c>
       <c r="B5" t="n">
-        <v>103774</v>
+        <v>103778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Thorell, Lennart Persson</t>
+          <t>Lennart Persson, Magnus Thorell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 23143-2024 artfynd.xlsx
+++ b/artfynd/A 23143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902885</v>
       </c>
       <c r="B2" t="n">
-        <v>105931</v>
+        <v>105944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902891</v>
       </c>
       <c r="B3" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125902848</v>
       </c>
       <c r="B4" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125902861</v>
       </c>
       <c r="B5" t="n">
-        <v>103778</v>
+        <v>103791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23143-2024 artfynd.xlsx
+++ b/artfynd/A 23143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902885</v>
       </c>
       <c r="B2" t="n">
-        <v>105944</v>
+        <v>105947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902891</v>
       </c>
       <c r="B3" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125902848</v>
       </c>
       <c r="B4" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125902861</v>
       </c>
       <c r="B5" t="n">
-        <v>103791</v>
+        <v>103794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23143-2024 artfynd.xlsx
+++ b/artfynd/A 23143-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125902885</v>
       </c>
       <c r="B2" t="n">
-        <v>105947</v>
+        <v>105956</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125902891</v>
       </c>
       <c r="B3" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125902848</v>
       </c>
       <c r="B4" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>125902861</v>
       </c>
       <c r="B5" t="n">
-        <v>103794</v>
+        <v>103803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
